--- a/Result/profitability/6121.xlsx
+++ b/Result/profitability/6121.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9975</v>
+        <v>7.16375</v>
       </c>
       <c r="N2" t="n">
-        <v>16.005</v>
+        <v>16.54125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.64</v>
       </c>
       <c r="M3" t="n">
-        <v>6.36125</v>
+        <v>6.45375</v>
       </c>
       <c r="N3" t="n">
-        <v>16.55125</v>
+        <v>16.87125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.3</v>
       </c>
       <c r="M4" t="n">
-        <v>5.733750000000001</v>
+        <v>5.898750000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>16.7825</v>
+        <v>17.09</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>3.11</v>
       </c>
       <c r="M5" t="n">
-        <v>5.155</v>
+        <v>5.581250000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>16.52125</v>
+        <v>17.03125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.02</v>
       </c>
       <c r="M6" t="n">
-        <v>4.701250000000001</v>
+        <v>4.85</v>
       </c>
       <c r="N6" t="n">
-        <v>16.85125</v>
+        <v>17.17875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.53</v>
       </c>
       <c r="M7" t="n">
-        <v>4.03375</v>
+        <v>3.99875</v>
       </c>
       <c r="N7" t="n">
-        <v>17.0475</v>
+        <v>17.34</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>3.09</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2525</v>
+        <v>3.53125</v>
       </c>
       <c r="N8" t="n">
-        <v>17.15625</v>
+        <v>17.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20917</v>
+      </c>
+      <c r="D75" t="n">
+        <v>17090</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3827</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2486</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>432</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2918</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1675</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7.817500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.9625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3265007320644218</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3500000000000014</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01949860724233998</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6035398230088496</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2869198312236287</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
